--- a/데이터/graduation_requirements_2023.xlsx
+++ b/데이터/graduation_requirements_2023.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\AI융개_팀플\데이터\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3215B396-422C-470B-AE3C-E93E85B13887}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트1" sheetId="1" r:id="rId5"/>
+    <sheet name="시트1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -88,9 +97,6 @@
     <t>융합보안공학과</t>
   </si>
   <si>
-    <t>청정융합에너지공학과</t>
-  </si>
-  <si>
     <t>일반화학 Ⅰ;일반화학 Ⅱ;일반물리학 Ⅰ</t>
   </si>
   <si>
@@ -113,23 +119,43 @@
   </si>
   <si>
     <t>바이오신약의과학부</t>
+  </si>
+  <si>
+    <t>청정신소재공학과</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="2">
@@ -137,70 +163,37 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -217,56 +210,80 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="시트1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="시트1-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:T9" displayName="표1" name="표1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:T9">
   <tableColumns count="20">
-    <tableColumn name="학과" id="1"/>
-    <tableColumn name="공통교양" id="2"/>
-    <tableColumn name="핵심교양" id="3"/>
-    <tableColumn name="진로소양" id="4"/>
-    <tableColumn name="교양합계" id="5"/>
-    <tableColumn name="핵심교양영역수" id="6"/>
-    <tableColumn name="자연의 설명 필수" id="7"/>
-    <tableColumn name="SW문해 필수" id="8"/>
-    <tableColumn name="필수 교양 과목" id="9"/>
-    <tableColumn name="핵심 전공" id="10"/>
-    <tableColumn name="심화 전공" id="11"/>
-    <tableColumn name="전공합계" id="12"/>
-    <tableColumn name="전공심화_핵심" id="13"/>
-    <tableColumn name="전공심화_심화" id="14"/>
-    <tableColumn name="전공심화_계" id="15"/>
-    <tableColumn name="부전공" id="16"/>
-    <tableColumn name="복수전공_핵심" id="17"/>
-    <tableColumn name="복수전공_심화" id="18"/>
-    <tableColumn name="복수전공_계" id="19"/>
-    <tableColumn name="총졸업학점" id="20"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="학과"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="공통교양"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="핵심교양"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="진로소양"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="교양합계"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="핵심교양영역수"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="자연의 설명 필수"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="SW문해 필수"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="필수 교양 과목"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="핵심 전공"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="심화 전공"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="전공합계"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="전공심화_핵심"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="전공심화_심화"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="전공심화_계"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="부전공"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="복수전공_핵심"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="복수전공_심화"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="복수전공_계"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="총졸업학점"/>
   </tableColumns>
-  <tableStyleInfo name="시트1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="시트1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -456,32 +473,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:T9"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.63"/>
-    <col customWidth="1" min="2" max="5" width="14.88"/>
-    <col customWidth="1" min="6" max="6" width="16.25"/>
-    <col customWidth="1" min="7" max="7" width="17.13"/>
-    <col customWidth="1" min="8" max="8" width="14.75"/>
-    <col customWidth="1" min="9" max="9" width="45.25"/>
-    <col customWidth="1" min="10" max="11" width="15.38"/>
-    <col customWidth="1" min="12" max="12" width="14.88"/>
-    <col customWidth="1" min="13" max="14" width="15.63"/>
-    <col customWidth="1" min="15" max="15" width="14.13"/>
-    <col customWidth="1" min="17" max="18" width="15.63"/>
-    <col customWidth="1" min="19" max="19" width="14.13"/>
-    <col customWidth="1" min="20" max="20" width="16.38"/>
+    <col min="1" max="1" width="17.6328125" customWidth="1"/>
+    <col min="2" max="5" width="14.90625" customWidth="1"/>
+    <col min="6" max="6" width="16.26953125" customWidth="1"/>
+    <col min="7" max="7" width="17.08984375" customWidth="1"/>
+    <col min="8" max="8" width="14.7265625" customWidth="1"/>
+    <col min="9" max="9" width="45.26953125" customWidth="1"/>
+    <col min="10" max="11" width="15.36328125" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" customWidth="1"/>
+    <col min="13" max="14" width="15.6328125" customWidth="1"/>
+    <col min="15" max="15" width="14.08984375" customWidth="1"/>
+    <col min="17" max="18" width="15.6328125" customWidth="1"/>
+    <col min="19" max="19" width="14.08984375" customWidth="1"/>
+    <col min="20" max="20" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,24 +563,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C2" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>33.0</v>
+      <c r="B2" s="2">
+        <v>15</v>
+      </c>
+      <c r="C2" s="2">
+        <v>15</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>33</v>
       </c>
       <c r="F2" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>21</v>
@@ -571,58 +591,58 @@
       <c r="I2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K2" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>48.0</v>
+      <c r="J2" s="2">
+        <v>27</v>
+      </c>
+      <c r="K2" s="2">
+        <v>21</v>
+      </c>
+      <c r="L2" s="2">
+        <v>48</v>
       </c>
       <c r="M2" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N2" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="O2" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="P2" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="2">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="R2" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="S2" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T2" s="3">
-        <v>130.0</v>
+        <v>45</v>
+      </c>
+      <c r="T2" s="2">
+        <v>130</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>33.0</v>
+      <c r="B3" s="2">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>33</v>
       </c>
       <c r="F3" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>21</v>
@@ -633,244 +653,244 @@
       <c r="I3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>48.0</v>
+      <c r="J3" s="2">
+        <v>27</v>
+      </c>
+      <c r="K3" s="2">
+        <v>21</v>
+      </c>
+      <c r="L3" s="2">
+        <v>48</v>
       </c>
       <c r="M3" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N3" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="O3" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="P3" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="Q3" s="2">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="R3" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="S3" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T3" s="3">
-        <v>130.0</v>
+        <v>45</v>
+      </c>
+      <c r="T3" s="2">
+        <v>130</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2">
+        <v>27</v>
+      </c>
+      <c r="K4" s="2">
+        <v>21</v>
+      </c>
+      <c r="L4" s="2">
+        <v>48</v>
+      </c>
+      <c r="M4" s="2">
+        <v>12</v>
+      </c>
+      <c r="N4" s="2">
+        <v>12</v>
+      </c>
+      <c r="O4" s="2">
+        <v>24</v>
+      </c>
+      <c r="P4" s="2">
+        <v>24</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>27</v>
+      </c>
+      <c r="R4" s="2">
+        <v>18</v>
+      </c>
+      <c r="S4" s="2">
+        <v>45</v>
+      </c>
+      <c r="T4" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>48.0</v>
-      </c>
-      <c r="M4" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="N4" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="O4" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="P4" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="R4" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="S4" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T4" s="3">
-        <v>130.0</v>
+      <c r="B5" s="2">
+        <v>15</v>
+      </c>
+      <c r="C5" s="2">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="2">
+        <v>27</v>
+      </c>
+      <c r="K5" s="2">
+        <v>21</v>
+      </c>
+      <c r="L5" s="2">
+        <v>48</v>
+      </c>
+      <c r="M5" s="2">
+        <v>12</v>
+      </c>
+      <c r="N5" s="2">
+        <v>12</v>
+      </c>
+      <c r="O5" s="2">
+        <v>24</v>
+      </c>
+      <c r="P5" s="2">
+        <v>24</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2">
+        <v>18</v>
+      </c>
+      <c r="S5" s="2">
+        <v>45</v>
+      </c>
+      <c r="T5" s="2">
+        <v>130</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>36.0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="2" t="s">
+    <row r="6" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K5" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L5" s="3">
-        <v>48.0</v>
-      </c>
-      <c r="M5" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="N5" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="O5" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="P5" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="R5" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="S5" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T5" s="3">
-        <v>130.0</v>
+      <c r="B6" s="2">
+        <v>15</v>
+      </c>
+      <c r="C6" s="2">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="2">
+        <v>27</v>
+      </c>
+      <c r="K6" s="2">
+        <v>21</v>
+      </c>
+      <c r="L6" s="2">
+        <v>48</v>
+      </c>
+      <c r="M6" s="2">
+        <v>12</v>
+      </c>
+      <c r="N6" s="2">
+        <v>12</v>
+      </c>
+      <c r="O6" s="2">
+        <v>24</v>
+      </c>
+      <c r="P6" s="2">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2">
+        <v>18</v>
+      </c>
+      <c r="S6" s="2">
+        <v>45</v>
+      </c>
+      <c r="T6" s="2">
+        <v>130</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>32.0</v>
-      </c>
-      <c r="F6" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="2" t="s">
+    <row r="7" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>48.0</v>
-      </c>
-      <c r="M6" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="N6" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="O6" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="P6" s="2">
-        <v>24.0</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>27.0</v>
-      </c>
-      <c r="R6" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="S6" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T6" s="3">
-        <v>130.0</v>
-      </c>
-    </row>
-    <row r="7" ht="22.5" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>33.0</v>
+      <c r="B7" s="2">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2">
+        <v>15</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>33</v>
       </c>
       <c r="F7" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>21</v>
@@ -881,58 +901,58 @@
       <c r="I7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J7" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L7" s="3">
-        <v>48.0</v>
+      <c r="J7" s="2">
+        <v>27</v>
+      </c>
+      <c r="K7" s="2">
+        <v>21</v>
+      </c>
+      <c r="L7" s="2">
+        <v>48</v>
       </c>
       <c r="M7" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N7" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="O7" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="P7" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="Q7" s="2">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="R7" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="S7" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T7" s="3">
-        <v>130.0</v>
+        <v>45</v>
+      </c>
+      <c r="T7" s="2">
+        <v>130</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>33.0</v>
+        <v>31</v>
+      </c>
+      <c r="B8" s="2">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2">
+        <v>15</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>33</v>
       </c>
       <c r="F8" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
@@ -943,58 +963,58 @@
       <c r="I8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>48.0</v>
+      <c r="J8" s="2">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2">
+        <v>21</v>
+      </c>
+      <c r="L8" s="2">
+        <v>48</v>
       </c>
       <c r="M8" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N8" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="O8" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="P8" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="Q8" s="2">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="R8" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="S8" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>130.0</v>
+        <v>45</v>
+      </c>
+      <c r="T8" s="2">
+        <v>130</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" spans="1:20" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>36.0</v>
+        <v>32</v>
+      </c>
+      <c r="B9" s="2">
+        <v>15</v>
+      </c>
+      <c r="C9" s="2">
+        <v>18</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>36</v>
       </c>
       <c r="F9" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>22</v>
@@ -1003,51 +1023,52 @@
         <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J9" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="L9" s="3">
-        <v>48.0</v>
+        <v>27</v>
+      </c>
+      <c r="J9" s="2">
+        <v>27</v>
+      </c>
+      <c r="K9" s="2">
+        <v>21</v>
+      </c>
+      <c r="L9" s="2">
+        <v>48</v>
       </c>
       <c r="M9" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="N9" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="O9" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="P9" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="Q9" s="2">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="R9" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="S9" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="T9" s="3">
-        <v>130.0</v>
+        <v>45</v>
+      </c>
+      <c r="T9" s="2">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="B2:E9 J2:L9 T2:T9">
+  <phoneticPr fontId="2" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="B2:E9 J2:L9 T2:T9" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>AND(ISNUMBER(B2),(NOT(OR(NOT(ISERROR(DATEVALUE(B2))), AND(ISNUMBER(B2), LEFT(CELL("format", B2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>